--- a/data/supplementary_tables/Supplementary Table 15.xlsx
+++ b/data/supplementary_tables/Supplementary Table 15.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Eukaryotes_Asgard_TACK/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_verified_red/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B9D9BD-710C-8C43-8906-30B4EABECADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76277264-8BB7-4547-B46F-901B2C4DC509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="222">
   <si>
     <t>Protein_Short_Name</t>
   </si>
@@ -79,12 +79,6 @@
     <t>CCR4-NOT transcription complex subunit 6</t>
   </si>
   <si>
-    <t>Mannose-6-phosphate Isomerase Type 2...</t>
-  </si>
-  <si>
-    <t>Haloacid dehalogenase domain protein...</t>
-  </si>
-  <si>
     <t>Heme-binding protein 1</t>
   </si>
   <si>
@@ -100,12 +94,6 @@
     <t>Xanthine uracil vitamin C permease</t>
   </si>
   <si>
-    <t>Binds double-stranded DNA tightly but</t>
-  </si>
-  <si>
-    <t>Proposed core component of the</t>
-  </si>
-  <si>
     <t>Eukaryotic Ribosomal Protein El38 Family</t>
   </si>
   <si>
@@ -118,30 +106,15 @@
     <t>Archaeal Rpom Eukaryotic RPA12 RPB9</t>
   </si>
   <si>
-    <t>Part of ribonuclease P, a protein complex</t>
-  </si>
-  <si>
     <t>Endoplasmic reticulum resident protein</t>
   </si>
   <si>
-    <t>Predicted SAM-dependent RNA...</t>
-  </si>
-  <si>
-    <t>Binds 16S rRNA</t>
-  </si>
-  <si>
     <t>Serine Threonine Protein Kinase</t>
   </si>
   <si>
     <t>Eukaryotic Ribosomal Protein El34 Family</t>
   </si>
   <si>
-    <t>Dual specificity protein phosphatase,...</t>
-  </si>
-  <si>
-    <t>Large family of predicted...</t>
-  </si>
-  <si>
     <t>Catalyzes the last two sequential</t>
   </si>
   <si>
@@ -211,9 +184,6 @@
     <t>TIGRFAM DMSO reductase family type</t>
   </si>
   <si>
-    <t>Could be</t>
-  </si>
-  <si>
     <t>PFAM Appr-1-p processing</t>
   </si>
   <si>
@@ -244,24 +214,9 @@
     <t>Ribosomal L22e protein family</t>
   </si>
   <si>
-    <t>Four repeated domains in the</t>
-  </si>
-  <si>
-    <t>Phosphatidylinositol glycan anchor...</t>
-  </si>
-  <si>
-    <t>Function in general translation initiation</t>
-  </si>
-  <si>
     <t>Gag-polyprotein Putative Aspartyl Protease</t>
   </si>
   <si>
-    <t>Catalyzes the phosphorylation of fructose</t>
-  </si>
-  <si>
-    <t>S-adenosyl-L-methionine-dependent...</t>
-  </si>
-  <si>
     <t>Sulphite efflux pump</t>
   </si>
   <si>
@@ -271,9 +226,6 @@
     <t>Replication factor-A C terminal domain</t>
   </si>
   <si>
-    <t>Gene with more than two</t>
-  </si>
-  <si>
     <t>Nitrogen Permease</t>
   </si>
   <si>
@@ -283,18 +235,12 @@
     <t>Aerotolerance regulator N-terminal</t>
   </si>
   <si>
-    <t>Molecular chaperone capable of stabilizing</t>
-  </si>
-  <si>
     <t>Tumor suppressor candidate 3</t>
   </si>
   <si>
     <t>Adapter protein</t>
   </si>
   <si>
-    <t>Binds directly to 23S rRNA.</t>
-  </si>
-  <si>
     <t>K02A2.6-like</t>
   </si>
   <si>
@@ -322,18 +268,9 @@
     <t>Zinc finger SWIM domain protein</t>
   </si>
   <si>
-    <t>Binds to 23S rRNA.</t>
-  </si>
-  <si>
-    <t>Reversibly transfers an adenylyl group</t>
-  </si>
-  <si>
     <t>Enzyme 2</t>
   </si>
   <si>
-    <t>DNA-damage inducible protein DDI1-like...</t>
-  </si>
-  <si>
     <t>Arrestin domain-containing protein 3</t>
   </si>
   <si>
@@ -349,9 +286,6 @@
     <t>Roadblock/LC7</t>
   </si>
   <si>
-    <t>Participates in various redox reactions</t>
-  </si>
-  <si>
     <t>NOSIC (NUC001) domain</t>
   </si>
   <si>
@@ -364,24 +298,9 @@
     <t>Amino Acid</t>
   </si>
   <si>
-    <t>Probable Brix domain-containing ribosomal...</t>
-  </si>
-  <si>
     <t>Pantothenate kinase</t>
   </si>
   <si>
-    <t>Serine protease with a broad</t>
-  </si>
-  <si>
-    <t>Involved in DNA repair and</t>
-  </si>
-  <si>
-    <t>Cytochrome c oxidase is the</t>
-  </si>
-  <si>
-    <t>Tubulin is the major constituent</t>
-  </si>
-  <si>
     <t>Binds to the 23S rRNA</t>
   </si>
   <si>
@@ -400,36 +319,18 @@
     <t>MCM family</t>
   </si>
   <si>
-    <t>Gamma-secretase Complex, An Endoprotease...</t>
-  </si>
-  <si>
     <t>Mediates influx of magnesium ions</t>
   </si>
   <si>
     <t>Anion-transporting ATPase</t>
   </si>
   <si>
-    <t>Galactinol--sucrose...</t>
-  </si>
-  <si>
     <t>RNA recognition motif</t>
   </si>
   <si>
-    <t>Adds a GMP to the</t>
-  </si>
-  <si>
     <t>Serine threonine protein kinase</t>
   </si>
   <si>
-    <t>Essential subunit of the N-oligosaccharyl</t>
-  </si>
-  <si>
-    <t>Catalyzes the ferrous insertion into</t>
-  </si>
-  <si>
-    <t>Catalyzes the interconversion of...</t>
-  </si>
-  <si>
     <t>Protein Phosphatase 1, Regulatory Subunit</t>
   </si>
   <si>
@@ -442,9 +343,6 @@
     <t>Ribosomal Protein S15</t>
   </si>
   <si>
-    <t>Natural Substrate for This Enzyme</t>
-  </si>
-  <si>
     <t>Eukaryotic Ribosomal Protein El18 Family</t>
   </si>
   <si>
@@ -454,9 +352,6 @@
     <t>GTP-binding protein 1</t>
   </si>
   <si>
-    <t>Retinal pigment epithelial membrane...</t>
-  </si>
-  <si>
     <t>Fibronectin Type III</t>
   </si>
   <si>
@@ -472,9 +367,6 @@
     <t>Major Facilitator Superfamily</t>
   </si>
   <si>
-    <t>Eca and bai are essential,</t>
-  </si>
-  <si>
     <t>PFAM Stem cell self-renewal protein Piwi</t>
   </si>
   <si>
@@ -490,45 +382,27 @@
     <t>Necrosis inducing protein (NPP1)</t>
   </si>
   <si>
-    <t>Asparagine Catabolic Process via...</t>
-  </si>
-  <si>
     <t>PFAM proteinase inhibitor I4 serpin</t>
   </si>
   <si>
     <t>Ligase 1</t>
   </si>
   <si>
-    <t>TIGRFAM ribosomal-protein-alanine...</t>
-  </si>
-  <si>
     <t>ATP-dependent DNA helicase</t>
   </si>
   <si>
-    <t>LDH MDH superfamily.</t>
-  </si>
-  <si>
     <t>Hydrolase</t>
   </si>
   <si>
     <t>TIGRFAM DNA polymerase (pol2)</t>
   </si>
   <si>
-    <t>Structure-specific nuclease with 5'-flap...</t>
-  </si>
-  <si>
-    <t>Permuted papain-like amidase enzyme,...</t>
-  </si>
-  <si>
     <t>General factor</t>
   </si>
   <si>
     <t>Transitional endoplasmic reticulum ATPase</t>
   </si>
   <si>
-    <t>Acts as a Ras effector</t>
-  </si>
-  <si>
     <t>Repeat Neuronal</t>
   </si>
   <si>
@@ -547,18 +421,9 @@
     <t>Uncharacterized protein family UPF0016</t>
   </si>
   <si>
-    <t>Involved in the binding of</t>
-  </si>
-  <si>
-    <t>Catalyzes the GTP-dependent ribosomal...</t>
-  </si>
-  <si>
     <t>Transposase-like protein</t>
   </si>
   <si>
-    <t>Cullin-associated NEDD8-dissociated...</t>
-  </si>
-  <si>
     <t>UPF0696 protein C11orf68 homolog</t>
   </si>
   <si>
@@ -568,27 +433,15 @@
     <t>GPN-loop GTPase 1</t>
   </si>
   <si>
-    <t>Serine-type Endopeptidase Activity.</t>
-  </si>
-  <si>
     <t>Cytoplasmic Translation</t>
   </si>
   <si>
-    <t>Sodium Neurotransmitter Symporter (snf)...</t>
-  </si>
-  <si>
-    <t>Class I-like Sam-binding...</t>
-  </si>
-  <si>
     <t>Glycosyl transferase family 2</t>
   </si>
   <si>
     <t>Translocon-associated protein</t>
   </si>
   <si>
-    <t>Involved in the secretory pathway</t>
-  </si>
-  <si>
     <t>Catalyzes the attachment of glycine</t>
   </si>
   <si>
@@ -610,18 +463,12 @@
     <t>Mediates zinc uptake.</t>
   </si>
   <si>
-    <t>Involved in pre-rRNA and tRNA processing.</t>
-  </si>
-  <si>
     <t>Methyltransferase</t>
   </si>
   <si>
     <t>Carboxypeptidase</t>
   </si>
   <si>
-    <t>Contacts the emerging nascent chain</t>
-  </si>
-  <si>
     <t>Stabilizes TBP binding to an</t>
   </si>
   <si>
@@ -634,21 +481,12 @@
     <t>DNA-directed RNA polymerases I, II,</t>
   </si>
   <si>
-    <t>Involved in the activation and</t>
-  </si>
-  <si>
     <t>'Cold-shock' DNA-binding domain</t>
   </si>
   <si>
     <t>Charged multivesicular body protein 2A</t>
   </si>
   <si>
-    <t>Methenyltetrahydrofolate Synthetase...</t>
-  </si>
-  <si>
-    <t>One of the primary rRNA binding proteins.</t>
-  </si>
-  <si>
     <t>Argonaute Family</t>
   </si>
   <si>
@@ -664,9 +502,6 @@
     <t>Acidic skeletal organic matrix protein</t>
   </si>
   <si>
-    <t>One of the primary rRNA</t>
-  </si>
-  <si>
     <t>Eif-2</t>
   </si>
   <si>
@@ -677,6 +512,180 @@
   </si>
   <si>
     <t>Supplementary Table 15 | ESP short names in TACK archaea: aggregated genome detection counts before and after decontamination and corresponding loss rates</t>
+  </si>
+  <si>
+    <t>Mannose-6-phosphate isomerase</t>
+  </si>
+  <si>
+    <t>HAD hydrolase</t>
+  </si>
+  <si>
+    <t>SAM-dependent RNA methyltransferase</t>
+  </si>
+  <si>
+    <t>Dual-specificity phosphatase</t>
+  </si>
+  <si>
+    <t>Nucleotide-binding domain protein</t>
+  </si>
+  <si>
+    <t>PIG-M</t>
+  </si>
+  <si>
+    <t>PIG-S</t>
+  </si>
+  <si>
+    <t>Diphthine synthase</t>
+  </si>
+  <si>
+    <t>TYW3</t>
+  </si>
+  <si>
+    <t>DDI1-like</t>
+  </si>
+  <si>
+    <t>Brix domain protein</t>
+  </si>
+  <si>
+    <t>γ-secretase subunit</t>
+  </si>
+  <si>
+    <t>Raffinose synthase-like</t>
+  </si>
+  <si>
+    <t>MTR-1-P isomerase</t>
+  </si>
+  <si>
+    <t>RPE membrane protein</t>
+  </si>
+  <si>
+    <t>Asparaginase</t>
+  </si>
+  <si>
+    <t>LDH MDH superfamily</t>
+  </si>
+  <si>
+    <t>RimI</t>
+  </si>
+  <si>
+    <t>FEN1</t>
+  </si>
+  <si>
+    <t>YaeF/YiiX (C92)</t>
+  </si>
+  <si>
+    <t>EF-G</t>
+  </si>
+  <si>
+    <t>CAND1</t>
+  </si>
+  <si>
+    <t>Serine-type Endopeptidase Activity</t>
+  </si>
+  <si>
+    <t>NSS / SNF transporter</t>
+  </si>
+  <si>
+    <t>RsmB / NOP2</t>
+  </si>
+  <si>
+    <t>MTHFS</t>
+  </si>
+  <si>
+    <t>Histone-like protein HU</t>
+  </si>
+  <si>
+    <t>INO80 complex subunit</t>
+  </si>
+  <si>
+    <t>RNase P subunit</t>
+  </si>
+  <si>
+    <t>30S assembly factor</t>
+  </si>
+  <si>
+    <t>tRNA pseudouridine synthase</t>
+  </si>
+  <si>
+    <t>Fasciclin domain protein</t>
+  </si>
+  <si>
+    <t>Translation initiation factor IF-2</t>
+  </si>
+  <si>
+    <t>ADP-dependent PFK</t>
+  </si>
+  <si>
+    <t>Multi-copy unassigned gene</t>
+  </si>
+  <si>
+    <t>HSP70-like chaperone</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L1</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L24</t>
+  </si>
+  <si>
+    <t>Ribosomal protein L14</t>
+  </si>
+  <si>
+    <t>Phosphopantetheine adenylyltransferase</t>
+  </si>
+  <si>
+    <t>Thioredoxin</t>
+  </si>
+  <si>
+    <t>RadA recombinase</t>
+  </si>
+  <si>
+    <t>Serine protease</t>
+  </si>
+  <si>
+    <t>Cytochrome c oxidase subunit I</t>
+  </si>
+  <si>
+    <t>Tubulin</t>
+  </si>
+  <si>
+    <t>tRNAᴴⁱˢ guanyltransferase</t>
+  </si>
+  <si>
+    <t>DV patterning factor</t>
+  </si>
+  <si>
+    <t>tRNA–ribosome binding factor</t>
+  </si>
+  <si>
+    <t>Exocyst subunit</t>
+  </si>
+  <si>
+    <t>Phytol kinase</t>
+  </si>
+  <si>
+    <t>Essential OST subunit mediating N-linked glycosylation</t>
+  </si>
+  <si>
+    <t>Catalyzes Fe²⁺ insertion into protoporphyrin IX</t>
+  </si>
+  <si>
+    <t>Acts on peptidyl-tRNAs released from ribosomes</t>
+  </si>
+  <si>
+    <t>Ras effector involved in MAPK pathway activation</t>
+  </si>
+  <si>
+    <t>Guide RNA-directed rRNA/tRNA 2'-O-methyltransferase</t>
+  </si>
+  <si>
+    <t>Binds the nascent polypeptide on the ribosome</t>
+  </si>
+  <si>
+    <t>Primary rRNA-binding protein required for 70S ribosome assembly and peptide bond formation</t>
+  </si>
+  <si>
+    <t>Primary rRNA-binding protein involved in early 50S ribosome assembly</t>
   </si>
 </sst>
 </file>
@@ -1049,18 +1058,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D217"/>
+  <dimension ref="A1:D220"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="28.6640625" style="1" customWidth="1"/>
     <col min="2" max="3" width="23.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27" style="1" customWidth="1"/>
+    <col min="4" max="4" width="41.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
-        <v>218</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -1289,7 +1298,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="1" t="s">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="B18" s="1">
         <v>6</v>
@@ -1303,7 +1312,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="B19" s="1">
         <v>25</v>
@@ -1317,7 +1326,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1">
         <v>11</v>
@@ -1331,7 +1340,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1">
         <v>12</v>
@@ -1345,7 +1354,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1">
         <v>14</v>
@@ -1359,7 +1368,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1">
         <v>14</v>
@@ -1373,7 +1382,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1">
         <v>23</v>
@@ -1387,7 +1396,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="1" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="B25" s="1">
         <v>28</v>
@@ -1401,7 +1410,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>191</v>
       </c>
       <c r="B26" s="1">
         <v>53</v>
@@ -1415,7 +1424,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B27" s="1">
         <v>181</v>
@@ -1429,7 +1438,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B28" s="1">
         <v>64</v>
@@ -1443,7 +1452,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B29" s="1">
         <v>71</v>
@@ -1457,7 +1466,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B30" s="1">
         <v>75</v>
@@ -1471,7 +1480,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" s="1" t="s">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="B31" s="1">
         <v>82</v>
@@ -1485,7 +1494,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B32" s="1">
         <v>161</v>
@@ -1499,7 +1508,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="1" t="s">
-        <v>34</v>
+        <v>166</v>
       </c>
       <c r="B33" s="1">
         <v>101</v>
@@ -1513,7 +1522,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="1" t="s">
-        <v>35</v>
+        <v>193</v>
       </c>
       <c r="B34" s="1">
         <v>317</v>
@@ -1527,7 +1536,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="B35" s="1">
         <v>348</v>
@@ -1541,7 +1550,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B36" s="1">
         <v>194</v>
@@ -1555,7 +1564,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="1" t="s">
-        <v>38</v>
+        <v>167</v>
       </c>
       <c r="B37" s="1">
         <v>209</v>
@@ -1569,7 +1578,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="1" t="s">
-        <v>39</v>
+        <v>168</v>
       </c>
       <c r="B38" s="1">
         <v>221</v>
@@ -1583,7 +1592,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B39" s="1">
         <v>224</v>
@@ -1597,7 +1606,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="B40" s="1">
         <v>408</v>
@@ -1611,7 +1620,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B41" s="1">
         <v>224</v>
@@ -1625,7 +1634,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B42" s="1">
         <v>192</v>
@@ -1639,7 +1648,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B43" s="1">
         <v>164</v>
@@ -1653,7 +1662,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" s="1" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B44" s="1">
         <v>104</v>
@@ -1667,7 +1676,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" s="1" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B45" s="1">
         <v>71</v>
@@ -1681,7 +1690,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="1" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B46" s="1">
         <v>65</v>
@@ -1695,7 +1704,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B47" s="1">
         <v>63</v>
@@ -1709,7 +1718,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" s="1" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B48" s="1">
         <v>58</v>
@@ -1723,7 +1732,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" s="1" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B49" s="1">
         <v>49</v>
@@ -1737,7 +1746,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B50" s="1">
         <v>48</v>
@@ -1751,7 +1760,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B51" s="1">
         <v>43</v>
@@ -1765,7 +1774,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" s="1" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B52" s="1">
         <v>40</v>
@@ -1779,7 +1788,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B53" s="1">
         <v>41</v>
@@ -1793,7 +1802,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B54" s="1">
         <v>34</v>
@@ -1807,7 +1816,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B55" s="1">
         <v>30</v>
@@ -1821,7 +1830,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B56" s="1">
         <v>29</v>
@@ -1835,7 +1844,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B57" s="1">
         <v>28</v>
@@ -1849,7 +1858,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B58" s="1">
         <v>27</v>
@@ -1863,7 +1872,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B59" s="1">
         <v>25</v>
@@ -1877,7 +1886,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B60" s="1">
         <v>23</v>
@@ -1891,7 +1900,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A61" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B61" s="1">
         <v>22</v>
@@ -1905,7 +1914,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A62" s="1" t="s">
-        <v>63</v>
+        <v>194</v>
       </c>
       <c r="B62" s="1">
         <v>20</v>
@@ -1919,7 +1928,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A63" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B63" s="1">
         <v>19</v>
@@ -1933,7 +1942,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A64" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B64" s="1">
         <v>19</v>
@@ -1947,7 +1956,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B65" s="1">
         <v>18</v>
@@ -1961,7 +1970,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B66" s="1">
         <v>18</v>
@@ -1975,7 +1984,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="1" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B67" s="1">
         <v>17</v>
@@ -1989,7 +1998,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B68" s="1">
         <v>17</v>
@@ -2003,7 +2012,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B69" s="1">
         <v>17</v>
@@ -2017,7 +2026,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" s="1" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B70" s="1">
         <v>16</v>
@@ -2031,7 +2040,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" s="1" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B71" s="1">
         <v>16</v>
@@ -2045,7 +2054,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A72" s="1" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B72" s="1">
         <v>14</v>
@@ -2059,7 +2068,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" s="1" t="s">
-        <v>74</v>
+        <v>195</v>
       </c>
       <c r="B73" s="1">
         <v>14</v>
@@ -2073,13 +2082,13 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" s="1" t="s">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="B74" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C74" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D74" s="5">
         <v>0</v>
@@ -2087,13 +2096,13 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" s="1" t="s">
-        <v>76</v>
+        <v>170</v>
       </c>
       <c r="B75" s="1">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C75" s="1">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D75" s="5">
         <v>0</v>
@@ -2101,13 +2110,13 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" s="1" t="s">
-        <v>77</v>
+        <v>196</v>
       </c>
       <c r="B76" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C76" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D76" s="5">
         <v>0</v>
@@ -2115,7 +2124,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B77" s="1">
         <v>13</v>
@@ -2129,13 +2138,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" s="1" t="s">
-        <v>79</v>
+        <v>197</v>
       </c>
       <c r="B78" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C78" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D78" s="5">
         <v>0</v>
@@ -2143,13 +2152,13 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" s="1" t="s">
-        <v>80</v>
+        <v>171</v>
       </c>
       <c r="B79" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C79" s="1">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D79" s="5">
         <v>0</v>
@@ -2157,13 +2166,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" s="1" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="B80" s="1">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C80" s="1">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D80" s="5">
         <v>0</v>
@@ -2171,7 +2180,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="1" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B81" s="1">
         <v>13</v>
@@ -2185,13 +2194,13 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" s="1" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B82" s="1">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C82" s="1">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D82" s="5">
         <v>0</v>
@@ -2199,13 +2208,13 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="1" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B83" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C83" s="1">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D83" s="5">
         <v>0</v>
@@ -2213,13 +2222,13 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="1" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="B84" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C84" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D84" s="5">
         <v>0</v>
@@ -2227,13 +2236,13 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="B85" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C85" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D85" s="5">
         <v>0</v>
@@ -2241,7 +2250,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="1" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="B86" s="1">
         <v>9</v>
@@ -2255,7 +2264,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="1" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="B87" s="1">
         <v>9</v>
@@ -2269,7 +2278,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="1" t="s">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="B88" s="1">
         <v>9</v>
@@ -2283,7 +2292,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B89" s="1">
         <v>9</v>
@@ -2297,7 +2306,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="B90" s="1">
         <v>9</v>
@@ -2311,13 +2320,13 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="1" t="s">
-        <v>92</v>
+        <v>200</v>
       </c>
       <c r="B91" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C91" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D91" s="5">
         <v>0</v>
@@ -2325,13 +2334,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="1" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="B92" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C92" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D92" s="5">
         <v>0</v>
@@ -2339,13 +2348,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="1" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B93" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C93" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D93" s="5">
         <v>0</v>
@@ -2353,7 +2362,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="1" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="B94" s="1">
         <v>7</v>
@@ -2367,7 +2376,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" s="1" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="B95" s="1">
         <v>7</v>
@@ -2381,7 +2390,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B96" s="1">
         <v>7</v>
@@ -2395,7 +2404,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="1" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="B97" s="1">
         <v>7</v>
@@ -2409,7 +2418,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="1" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="B98" s="1">
         <v>7</v>
@@ -2423,13 +2432,13 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="1" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="B99" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C99" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D99" s="5">
         <v>0</v>
@@ -2437,13 +2446,13 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" s="1" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="B100" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C100" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D100" s="5">
         <v>0</v>
@@ -2451,7 +2460,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" s="1" t="s">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="B101" s="1">
         <v>6</v>
@@ -2465,13 +2474,13 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" s="1" t="s">
-        <v>103</v>
+        <v>202</v>
       </c>
       <c r="B102" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C102" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D102" s="5">
         <v>0</v>
@@ -2479,7 +2488,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" s="1" t="s">
-        <v>104</v>
+        <v>203</v>
       </c>
       <c r="B103" s="1">
         <v>6</v>
@@ -2493,7 +2502,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" s="1" t="s">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="B104" s="1">
         <v>6</v>
@@ -2507,7 +2516,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" s="1" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="B105" s="1">
         <v>6</v>
@@ -2521,13 +2530,13 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" s="1" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="B106" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C106" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D106" s="5">
         <v>0</v>
@@ -2535,13 +2544,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A107" s="1" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="B107" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C107" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D107" s="5">
         <v>0</v>
@@ -2549,13 +2558,13 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A108" s="1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="B108" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C108" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D108" s="5">
         <v>0</v>
@@ -2563,7 +2572,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A109" s="1" t="s">
-        <v>217</v>
+        <v>86</v>
       </c>
       <c r="B109" s="1">
         <v>5</v>
@@ -2577,7 +2586,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A110" s="1" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="B110" s="1">
         <v>5</v>
@@ -2591,7 +2600,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A111" s="1" t="s">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="B111" s="1">
         <v>5</v>
@@ -2605,7 +2614,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="B112" s="1">
         <v>5</v>
@@ -2619,13 +2628,13 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A113" s="1" t="s">
-        <v>113</v>
+        <v>88</v>
       </c>
       <c r="B113" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C113" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D113" s="5">
         <v>0</v>
@@ -2633,13 +2642,13 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A114" s="1" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="B114" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C114" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D114" s="5">
         <v>0</v>
@@ -2647,13 +2656,13 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A115" s="1" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="B115" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C115" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D115" s="5">
         <v>0</v>
@@ -2661,7 +2670,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A116" s="1" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="B116" s="1">
         <v>4</v>
@@ -2675,7 +2684,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A117" s="1" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="B117" s="1">
         <v>4</v>
@@ -2689,7 +2698,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A118" s="1" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="B118" s="1">
         <v>4</v>
@@ -2703,13 +2712,13 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A119" s="1" t="s">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="B119" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C119" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D119" s="5">
         <v>0</v>
@@ -2717,13 +2726,13 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A120" s="1" t="s">
-        <v>120</v>
+        <v>205</v>
       </c>
       <c r="B120" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C120" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D120" s="5">
         <v>0</v>
@@ -2731,13 +2740,13 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A121" s="1" t="s">
-        <v>121</v>
+        <v>207</v>
       </c>
       <c r="B121" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C121" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D121" s="5">
         <v>0</v>
@@ -2745,7 +2754,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A122" s="1" t="s">
-        <v>122</v>
+        <v>208</v>
       </c>
       <c r="B122" s="1">
         <v>3</v>
@@ -2759,7 +2768,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A123" s="1" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="B123" s="1">
         <v>3</v>
@@ -2773,7 +2782,7 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A124" s="1" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="B124" s="1">
         <v>3</v>
@@ -2787,13 +2796,13 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A125" s="1" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="B125" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C125" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D125" s="5">
         <v>0</v>
@@ -2801,7 +2810,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A126" s="1" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="B126" s="1">
         <v>3</v>
@@ -2815,7 +2824,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A127" s="1" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="B127" s="1">
         <v>3</v>
@@ -2829,13 +2838,13 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A128" s="1" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="B128" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C128" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D128" s="5">
         <v>0</v>
@@ -2843,7 +2852,7 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="B129" s="1">
         <v>3</v>
@@ -2857,13 +2866,13 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A130" s="1" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="B130" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C130" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D130" s="5">
         <v>0</v>
@@ -2871,13 +2880,13 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A131" s="1" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="B131" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C131" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D131" s="5">
         <v>0</v>
@@ -2885,13 +2894,13 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A132" s="1" t="s">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="B132" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C132" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D132" s="5">
         <v>0</v>
@@ -2899,7 +2908,7 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A133" s="1" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="B133" s="1">
         <v>2</v>
@@ -2913,7 +2922,7 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A134" s="1" t="s">
-        <v>134</v>
+        <v>209</v>
       </c>
       <c r="B134" s="1">
         <v>2</v>
@@ -2927,7 +2936,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A135" s="1" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="B135" s="1">
         <v>2</v>
@@ -2941,7 +2950,7 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A136" s="1" t="s">
-        <v>136</v>
+        <v>214</v>
       </c>
       <c r="B136" s="1">
         <v>2</v>
@@ -2955,7 +2964,7 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A137" s="1" t="s">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="B137" s="1">
         <v>2</v>
@@ -2969,7 +2978,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A138" s="1" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="B138" s="1">
         <v>2</v>
@@ -2983,7 +2992,7 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A139" s="1" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="B139" s="1">
         <v>2</v>
@@ -2997,7 +3006,7 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A140" s="1" t="s">
-        <v>140</v>
+        <v>104</v>
       </c>
       <c r="B140" s="1">
         <v>2</v>
@@ -3011,7 +3020,7 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A141" s="1" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="B141" s="1">
         <v>2</v>
@@ -3025,7 +3034,7 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A142" s="1" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="B142" s="1">
         <v>2</v>
@@ -3039,7 +3048,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A143" s="1" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="B143" s="1">
         <v>2</v>
@@ -3053,7 +3062,7 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A144" s="1" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="B144" s="1">
         <v>2</v>
@@ -3067,7 +3076,7 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A145" s="1" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="B145" s="1">
         <v>2</v>
@@ -3081,7 +3090,7 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A146" s="1" t="s">
-        <v>146</v>
+        <v>109</v>
       </c>
       <c r="B146" s="1">
         <v>2</v>
@@ -3095,7 +3104,7 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A147" s="1" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="B147" s="1">
         <v>2</v>
@@ -3109,7 +3118,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A148" s="1" t="s">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="B148" s="1">
         <v>2</v>
@@ -3123,7 +3132,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A149" s="1" t="s">
-        <v>149</v>
+        <v>111</v>
       </c>
       <c r="B149" s="1">
         <v>2</v>
@@ -3137,7 +3146,7 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A150" s="1" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="B150" s="1">
         <v>2</v>
@@ -3151,7 +3160,7 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A151" s="1" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="B151" s="1">
         <v>2</v>
@@ -3165,7 +3174,7 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A152" s="1" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="B152" s="1">
         <v>2</v>
@@ -3179,13 +3188,13 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A153" s="1" t="s">
-        <v>153</v>
+        <v>210</v>
       </c>
       <c r="B153" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C153" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D153" s="5">
         <v>0</v>
@@ -3193,13 +3202,13 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A154" s="1" t="s">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="B154" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C154" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D154" s="5">
         <v>0</v>
@@ -3207,7 +3216,7 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A155" s="1" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="B155" s="1">
         <v>2</v>
@@ -3221,7 +3230,7 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A156" s="1" t="s">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="B156" s="1">
         <v>1</v>
@@ -3235,7 +3244,7 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A157" s="1" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="B157" s="1">
         <v>1</v>
@@ -3249,13 +3258,13 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A158" s="1" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="B158" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C158" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D158" s="5">
         <v>0</v>
@@ -3263,7 +3272,7 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A159" s="1" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="B159" s="1">
         <v>1</v>
@@ -3277,7 +3286,7 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A160" s="1" t="s">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="B160" s="1">
         <v>1</v>
@@ -3291,7 +3300,7 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A161" s="1" t="s">
-        <v>161</v>
+        <v>121</v>
       </c>
       <c r="B161" s="1">
         <v>1</v>
@@ -3305,7 +3314,7 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A162" s="1" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="B162" s="1">
         <v>1</v>
@@ -3319,13 +3328,13 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A163" s="1" t="s">
-        <v>163</v>
+        <v>122</v>
       </c>
       <c r="B163" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C163" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" s="5">
         <v>0</v>
@@ -3333,7 +3342,7 @@
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A164" s="1" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="B164" s="1">
         <v>1</v>
@@ -3347,7 +3356,7 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A165" s="1" t="s">
-        <v>165</v>
+        <v>123</v>
       </c>
       <c r="B165" s="1">
         <v>1</v>
@@ -3361,13 +3370,13 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A166" s="1" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="B166" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C166" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D166" s="5">
         <v>0</v>
@@ -3375,7 +3384,7 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A167" s="1" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B167" s="1">
         <v>1</v>
@@ -3389,7 +3398,7 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A168" s="1" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B168" s="1">
         <v>1</v>
@@ -3403,7 +3412,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A169" s="1" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="B169" s="1">
         <v>1</v>
@@ -3417,7 +3426,7 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A170" s="1" t="s">
-        <v>170</v>
+        <v>126</v>
       </c>
       <c r="B170" s="1">
         <v>1</v>
@@ -3431,7 +3440,7 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A171" s="1" t="s">
-        <v>171</v>
+        <v>217</v>
       </c>
       <c r="B171" s="1">
         <v>1</v>
@@ -3445,7 +3454,7 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A172" s="1" t="s">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="B172" s="1">
         <v>1</v>
@@ -3459,7 +3468,7 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A173" s="1" t="s">
-        <v>173</v>
+        <v>128</v>
       </c>
       <c r="B173" s="1">
         <v>1</v>
@@ -3473,7 +3482,7 @@
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A174" s="1" t="s">
-        <v>174</v>
+        <v>129</v>
       </c>
       <c r="B174" s="1">
         <v>1</v>
@@ -3487,7 +3496,7 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A175" s="1" t="s">
-        <v>175</v>
+        <v>130</v>
       </c>
       <c r="B175" s="1">
         <v>1</v>
@@ -3501,7 +3510,7 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A176" s="1" t="s">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="B176" s="1">
         <v>1</v>
@@ -3515,7 +3524,7 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A177" s="1" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="B177" s="1">
         <v>1</v>
@@ -3529,7 +3538,7 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A178" s="1" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="B178" s="1">
         <v>1</v>
@@ -3543,7 +3552,7 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A179" s="1" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B179" s="1">
         <v>1</v>
@@ -3557,7 +3566,7 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A180" s="1" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="B180" s="1">
         <v>1</v>
@@ -3571,7 +3580,7 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A181" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B181" s="1">
         <v>1</v>
@@ -3585,7 +3594,7 @@
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A182" s="1" t="s">
-        <v>182</v>
+        <v>134</v>
       </c>
       <c r="B182" s="1">
         <v>1</v>
@@ -3599,7 +3608,7 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A183" s="1" t="s">
-        <v>183</v>
+        <v>135</v>
       </c>
       <c r="B183" s="1">
         <v>1</v>
@@ -3613,7 +3622,7 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A184" s="1" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="B184" s="1">
         <v>1</v>
@@ -3627,7 +3636,7 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A185" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B185" s="1">
         <v>1</v>
@@ -3641,7 +3650,7 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A186" s="1" t="s">
-        <v>186</v>
+        <v>137</v>
       </c>
       <c r="B186" s="1">
         <v>1</v>
@@ -3683,7 +3692,7 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A189" s="1" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="B189" s="1">
         <v>1</v>
@@ -3697,7 +3706,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A190" s="1" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="B190" s="1">
         <v>1</v>
@@ -3711,7 +3720,7 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A191" s="1" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="B191" s="1">
         <v>1</v>
@@ -3725,7 +3734,7 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A192" s="1" t="s">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="B192" s="1">
         <v>1</v>
@@ -3739,7 +3748,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A193" s="1" t="s">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="B193" s="1">
         <v>1</v>
@@ -3753,7 +3762,7 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A194" s="1" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="B194" s="1">
         <v>1</v>
@@ -3767,7 +3776,7 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A195" s="1" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
       <c r="B195" s="1">
         <v>1</v>
@@ -3781,7 +3790,7 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A196" s="1" t="s">
-        <v>196</v>
+        <v>144</v>
       </c>
       <c r="B196" s="1">
         <v>1</v>
@@ -3795,7 +3804,7 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A197" s="1" t="s">
-        <v>197</v>
+        <v>145</v>
       </c>
       <c r="B197" s="1">
         <v>1</v>
@@ -3809,7 +3818,7 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A198" s="1" t="s">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="B198" s="1">
         <v>1</v>
@@ -3823,7 +3832,7 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A199" s="1" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="B199" s="1">
         <v>1</v>
@@ -3837,7 +3846,7 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A200" s="1" t="s">
-        <v>216</v>
+        <v>147</v>
       </c>
       <c r="B200" s="1">
         <v>1</v>
@@ -3851,7 +3860,7 @@
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A201" s="1" t="s">
-        <v>200</v>
+        <v>148</v>
       </c>
       <c r="B201" s="1">
         <v>1</v>
@@ -3865,7 +3874,7 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A202" s="1" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="B202" s="1">
         <v>1</v>
@@ -3879,7 +3888,7 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A203" s="1" t="s">
-        <v>202</v>
+        <v>161</v>
       </c>
       <c r="B203" s="1">
         <v>1</v>
@@ -3893,7 +3902,7 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A204" s="1" t="s">
-        <v>203</v>
+        <v>149</v>
       </c>
       <c r="B204" s="1">
         <v>1</v>
@@ -3907,7 +3916,7 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A205" s="1" t="s">
-        <v>204</v>
+        <v>150</v>
       </c>
       <c r="B205" s="1">
         <v>1</v>
@@ -3921,7 +3930,7 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A206" s="1" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="B206" s="1">
         <v>1</v>
@@ -3935,7 +3944,7 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A207" s="1" t="s">
-        <v>206</v>
+        <v>152</v>
       </c>
       <c r="B207" s="1">
         <v>1</v>
@@ -3949,7 +3958,7 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A208" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B208" s="1">
         <v>1</v>
@@ -3963,7 +3972,7 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A209" s="1" t="s">
-        <v>208</v>
+        <v>153</v>
       </c>
       <c r="B209" s="1">
         <v>1</v>
@@ -3977,7 +3986,7 @@
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A210" s="1" t="s">
-        <v>209</v>
+        <v>154</v>
       </c>
       <c r="B210" s="1">
         <v>1</v>
@@ -3991,7 +4000,7 @@
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A211" s="1" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="B211" s="1">
         <v>1</v>
@@ -4005,7 +4014,7 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A212" s="1" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B212" s="1">
         <v>1</v>
@@ -4019,7 +4028,7 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A213" s="1" t="s">
-        <v>212</v>
+        <v>155</v>
       </c>
       <c r="B213" s="1">
         <v>1</v>
@@ -4033,7 +4042,7 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A214" s="1" t="s">
-        <v>213</v>
+        <v>156</v>
       </c>
       <c r="B214" s="1">
         <v>1</v>
@@ -4047,7 +4056,7 @@
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A215" s="1" t="s">
-        <v>214</v>
+        <v>157</v>
       </c>
       <c r="B215" s="1">
         <v>1</v>
@@ -4059,21 +4068,63 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="B216" s="4">
-        <v>1</v>
-      </c>
-      <c r="C216" s="4">
-        <v>1</v>
-      </c>
-      <c r="D216" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.15"/>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A216" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B216" s="1">
+        <v>1</v>
+      </c>
+      <c r="C216" s="1">
+        <v>1</v>
+      </c>
+      <c r="D216" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A217" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B217" s="1">
+        <v>1</v>
+      </c>
+      <c r="C217" s="1">
+        <v>1</v>
+      </c>
+      <c r="D217" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A218" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B218" s="1">
+        <v>1</v>
+      </c>
+      <c r="C218" s="1">
+        <v>1</v>
+      </c>
+      <c r="D218" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A219" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B219" s="4">
+        <v>1</v>
+      </c>
+      <c r="C219" s="4">
+        <v>1</v>
+      </c>
+      <c r="D219" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
